--- a/artfynd/A 26271-2026 artfynd.xlsx
+++ b/artfynd/A 26271-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135669297</v>
       </c>
       <c r="B2" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>135669298</v>
       </c>
       <c r="B3" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26271-2026 artfynd.xlsx
+++ b/artfynd/A 26271-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135669297</v>
       </c>
       <c r="B2" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>135669298</v>
       </c>
       <c r="B3" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26271-2026 artfynd.xlsx
+++ b/artfynd/A 26271-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135669297</v>
       </c>
       <c r="B2" t="n">
-        <v>99211</v>
+        <v>99212</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>135669298</v>
       </c>
       <c r="B3" t="n">
-        <v>99211</v>
+        <v>99212</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26271-2026 artfynd.xlsx
+++ b/artfynd/A 26271-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135669297</v>
       </c>
       <c r="B2" t="n">
-        <v>99212</v>
+        <v>99213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>135669298</v>
       </c>
       <c r="B3" t="n">
-        <v>99212</v>
+        <v>99213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26271-2026 artfynd.xlsx
+++ b/artfynd/A 26271-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135669297</v>
       </c>
       <c r="B2" t="n">
-        <v>99213</v>
+        <v>99219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>135669298</v>
       </c>
       <c r="B3" t="n">
-        <v>99213</v>
+        <v>99219</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26271-2026 artfynd.xlsx
+++ b/artfynd/A 26271-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135669297</v>
       </c>
       <c r="B2" t="n">
-        <v>99219</v>
+        <v>99220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>135669298</v>
       </c>
       <c r="B3" t="n">
-        <v>99219</v>
+        <v>99220</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26271-2026 artfynd.xlsx
+++ b/artfynd/A 26271-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135669297</v>
       </c>
       <c r="B2" t="n">
-        <v>99220</v>
+        <v>99231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>135669298</v>
       </c>
       <c r="B3" t="n">
-        <v>99220</v>
+        <v>99231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26271-2026 artfynd.xlsx
+++ b/artfynd/A 26271-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135669297</v>
       </c>
       <c r="B2" t="n">
-        <v>99231</v>
+        <v>99244</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>135669298</v>
       </c>
       <c r="B3" t="n">
-        <v>99231</v>
+        <v>99244</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26271-2026 artfynd.xlsx
+++ b/artfynd/A 26271-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135669297</v>
       </c>
       <c r="B2" t="n">
-        <v>99244</v>
+        <v>99245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>135669298</v>
       </c>
       <c r="B3" t="n">
-        <v>99244</v>
+        <v>99245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26271-2026 artfynd.xlsx
+++ b/artfynd/A 26271-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135669297</v>
       </c>
       <c r="B2" t="n">
-        <v>99245</v>
+        <v>99258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>135669298</v>
       </c>
       <c r="B3" t="n">
-        <v>99245</v>
+        <v>99258</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26271-2026 artfynd.xlsx
+++ b/artfynd/A 26271-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135669297</v>
       </c>
       <c r="B2" t="n">
-        <v>99258</v>
+        <v>99259</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>135669298</v>
       </c>
       <c r="B3" t="n">
-        <v>99258</v>
+        <v>99259</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
